--- a/FinalReport/Evidence/wav2vec_vs_mfcc/wav2vec_irish_summary.xlsx
+++ b/FinalReport/Evidence/wav2vec_vs_mfcc/wav2vec_irish_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cianan/Documents/College/GitHub/FYP/Experiments/AutoWav2VecIrish/results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cianan/Documents/College/GitHub/FYP/FinalReport/Evidence/wav2vec_vs_mfcc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E2C8F8-C25D-2E4D-AE62-EFB1CC170667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640B1513-AC2E-4848-8F93-05C07CC81049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1500" windowWidth="34560" windowHeight="19960" activeTab="5" xr2:uid="{246BDAFC-0F62-D04B-9CBE-61D931EE4911}"/>
+    <workbookView xWindow="0" yWindow="1960" windowWidth="34560" windowHeight="19960" activeTab="5" xr2:uid="{246BDAFC-0F62-D04B-9CBE-61D931EE4911}"/>
   </bookViews>
   <sheets>
     <sheet name="wav2vec_irish_summary" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="60">
   <si>
     <t>task_name</t>
   </si>
@@ -212,6 +212,12 @@
   </si>
   <si>
     <t>Ulster vs Rest</t>
+  </si>
+  <si>
+    <t>RelativeImprovement Wav2vec</t>
+  </si>
+  <si>
+    <t>RelativeImprovement MFCC</t>
   </si>
 </sst>
 </file>
@@ -886,7 +892,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
@@ -939,6 +945,17 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="35" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="35" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -37086,10 +37103,9 @@
     <col min="17" max="17" width="21.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.83203125" customWidth="1"/>
     <col min="21" max="21" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="27" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9.5" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="12.5" bestFit="1" customWidth="1"/>
@@ -37183,23 +37199,21 @@
       <c r="Q1" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="R1" s="26" t="s">
-        <v>0</v>
-      </c>
+      <c r="R1" s="26"/>
       <c r="S1" s="31" t="s">
         <v>32</v>
       </c>
       <c r="T1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="V1" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="W1" s="31" t="s">
-        <v>3</v>
+      <c r="U1" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="V1" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="W1" s="46" t="s">
+        <v>59</v>
       </c>
       <c r="X1" s="31" t="s">
         <v>4</v>
@@ -37375,6 +37389,18 @@
         <f>(Table21[[#This Row],[balanced_accuracy_mean]]-Table21[[#This Row],[baseline]])/Table21[[#This Row],[baseline]]</f>
         <v>0.36192950984118011</v>
       </c>
+      <c r="U2" s="50" t="str">
+        <f>Table21[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table21[[#This Row],[model_name_better]]</f>
+        <v>Leinster vs Rest
+Logistic Regression (Weighted)</v>
+      </c>
+      <c r="V2" s="47">
+        <f>(Table21[[#This Row],[balanced_accuracy_mean]]-Table21[[#This Row],[baseline]])/Table21[[#This Row],[baseline]]</f>
+        <v>0.36192950984118011</v>
+      </c>
+      <c r="W2" s="52">
+        <v>0.2316</v>
+      </c>
     </row>
     <row r="3" spans="1:64" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
@@ -37431,6 +37457,15 @@
         <f>(Table21[[#This Row],[balanced_accuracy_mean]]-Table21[[#This Row],[baseline]])/Table21[[#This Row],[baseline]]</f>
         <v>0.56875046258539808</v>
       </c>
+      <c r="U3" s="51" t="str">
+        <f>Table21[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table21[[#This Row],[model_name_better]]</f>
+        <v>Ulster vs Rest
+Random Forest</v>
+      </c>
+      <c r="V3" s="48">
+        <f>(Table21[[#This Row],[balanced_accuracy_mean]]-Table21[[#This Row],[baseline]])/Table21[[#This Row],[baseline]]</f>
+        <v>0.56875046258539808</v>
+      </c>
     </row>
     <row r="4" spans="1:64" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
@@ -37487,6 +37522,15 @@
         <f>(Table21[[#This Row],[balanced_accuracy_mean]]-Table21[[#This Row],[baseline]])/Table21[[#This Row],[baseline]]</f>
         <v>0.79009262318694806</v>
       </c>
+      <c r="U4" s="50" t="str">
+        <f>Table21[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table21[[#This Row],[model_name_better]]</f>
+        <v xml:space="preserve">Ulster, Leinster, and Rest
+Logistic Regression </v>
+      </c>
+      <c r="V4" s="47">
+        <f>(Table21[[#This Row],[balanced_accuracy_mean]]-Table21[[#This Row],[baseline]])/Table21[[#This Row],[baseline]]</f>
+        <v>0.79009262318694806</v>
+      </c>
     </row>
     <row r="5" spans="1:64" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
@@ -37540,6 +37584,15 @@
         <v>0</v>
       </c>
       <c r="Q5" s="41">
+        <f>(Table21[[#This Row],[balanced_accuracy_mean]]-Table21[[#This Row],[baseline]])/Table21[[#This Row],[baseline]]</f>
+        <v>0.86392249287122391</v>
+      </c>
+      <c r="U5" s="51" t="str">
+        <f>Table21[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table21[[#This Row],[model_name_better]]</f>
+        <v xml:space="preserve">Four Provinces
+Logistic Regression </v>
+      </c>
+      <c r="V5" s="49">
         <f>(Table21[[#This Row],[balanced_accuracy_mean]]-Table21[[#This Row],[baseline]])/Table21[[#This Row],[baseline]]</f>
         <v>0.86392249287122391</v>
       </c>
